--- a/ig/nr-prepare-ballot-3/StructureDefinition-as-practitioner.xlsx
+++ b/ig/nr-prepare-ballot-3/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T16:53:53+00:00</t>
+    <t>2023-12-19T08:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
